--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/120.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/120.xlsx
@@ -426,13 +426,13 @@
         <v>-9.356851648780063</v>
       </c>
       <c r="E2">
-        <v>-18.30408948723718</v>
+        <v>-19.61164560068593</v>
       </c>
       <c r="F2">
-        <v>-0.7055811350322511</v>
+        <v>-2.031434521991833</v>
       </c>
       <c r="G2">
-        <v>-11.75293749153919</v>
+        <v>-11.09158103646064</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.757185231632132</v>
       </c>
       <c r="E3">
-        <v>-18.82532590246805</v>
+        <v>-19.42735029399577</v>
       </c>
       <c r="F3">
-        <v>-0.6718036258156984</v>
+        <v>-1.494839656010786</v>
       </c>
       <c r="G3">
-        <v>-11.87638032782706</v>
+        <v>-10.26391586664162</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.046243491744926</v>
       </c>
       <c r="E4">
-        <v>-19.4085390129679</v>
+        <v>-19.09924876671802</v>
       </c>
       <c r="F4">
-        <v>-1.009487597566917</v>
+        <v>-1.172947680426538</v>
       </c>
       <c r="G4">
-        <v>-11.03711275857385</v>
+        <v>-9.078095519944542</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.297809415215196</v>
       </c>
       <c r="E5">
-        <v>-19.31402070347981</v>
+        <v>-18.78134536290556</v>
       </c>
       <c r="F5">
-        <v>-0.6237831674754111</v>
+        <v>-2.033217168642658</v>
       </c>
       <c r="G5">
-        <v>-10.81457703119075</v>
+        <v>-9.820619552739084</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-6.525991289801186</v>
       </c>
       <c r="E6">
-        <v>-19.50027683941529</v>
+        <v>-21.20894706656744</v>
       </c>
       <c r="F6">
-        <v>-0.754491259963145</v>
+        <v>-1.424170804510558</v>
       </c>
       <c r="G6">
-        <v>-10.43668202541107</v>
+        <v>-9.318887964084391</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-5.773932133954851</v>
       </c>
       <c r="E7">
-        <v>-21.85911819374471</v>
+        <v>-20.84866167451719</v>
       </c>
       <c r="F7">
-        <v>-0.7296435513487711</v>
+        <v>-1.374853951184889</v>
       </c>
       <c r="G7">
-        <v>-10.2308509969871</v>
+        <v>-8.846034406374374</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.055767110891066</v>
       </c>
       <c r="E8">
-        <v>-20.84936358798838</v>
+        <v>-21.63929700846437</v>
       </c>
       <c r="F8">
-        <v>-0.7824784810341292</v>
+        <v>-1.47201813406366</v>
       </c>
       <c r="G8">
-        <v>-9.380679928491855</v>
+        <v>-8.676159003798801</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-4.404721332003176</v>
       </c>
       <c r="E9">
-        <v>-21.81365684318171</v>
+        <v>-22.16783332379561</v>
       </c>
       <c r="F9">
-        <v>-0.8708288347471133</v>
+        <v>-1.734308246649082</v>
       </c>
       <c r="G9">
-        <v>-9.042448328922733</v>
+        <v>-8.565234027760214</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-3.828520457998938</v>
       </c>
       <c r="E10">
-        <v>-22.87082004332434</v>
+        <v>-22.89999247288175</v>
       </c>
       <c r="F10">
-        <v>-0.6904601164615489</v>
+        <v>-1.556683081201589</v>
       </c>
       <c r="G10">
-        <v>-9.101999219005096</v>
+        <v>-8.973667362593654</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-3.34105677041024</v>
       </c>
       <c r="E11">
-        <v>-22.32667860656267</v>
+        <v>-22.19499058241961</v>
       </c>
       <c r="F11">
-        <v>-0.3282655816288959</v>
+        <v>-1.024451226331087</v>
       </c>
       <c r="G11">
-        <v>-9.07864020272341</v>
+        <v>-9.057502573437466</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-2.947516788818342</v>
       </c>
       <c r="E12">
-        <v>-23.46783594259956</v>
+        <v>-23.53732537624727</v>
       </c>
       <c r="F12">
-        <v>-0.6907251940304447</v>
+        <v>-1.366846951869429</v>
       </c>
       <c r="G12">
-        <v>-7.498653272533351</v>
+        <v>-7.649254779668745</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-2.642443305381311</v>
       </c>
       <c r="E13">
-        <v>-24.10454844502603</v>
+        <v>-25.03099724293726</v>
       </c>
       <c r="F13">
-        <v>-0.2106200147159072</v>
+        <v>-1.297592123525779</v>
       </c>
       <c r="G13">
-        <v>-8.845496286038625</v>
+        <v>-8.147547648129139</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.430652340707331</v>
       </c>
       <c r="E14">
-        <v>-24.90811257226511</v>
+        <v>-23.88859457654825</v>
       </c>
       <c r="F14">
-        <v>-0.101467698783822</v>
+        <v>-0.9030978869231679</v>
       </c>
       <c r="G14">
-        <v>-7.856004550129357</v>
+        <v>-6.951863949424365</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.297786980043203</v>
       </c>
       <c r="E15">
-        <v>-25.18967044369202</v>
+        <v>-26.51150483568695</v>
       </c>
       <c r="F15">
-        <v>0.2200771908586537</v>
+        <v>-0.646680899223595</v>
       </c>
       <c r="G15">
-        <v>-7.859748423928683</v>
+        <v>-6.923035136803084</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.240001706590901</v>
       </c>
       <c r="E16">
-        <v>-26.22392862230385</v>
+        <v>-25.27318003286747</v>
       </c>
       <c r="F16">
-        <v>0.5535762504909291</v>
+        <v>-0.3938449438063243</v>
       </c>
       <c r="G16">
-        <v>-7.732925929434585</v>
+        <v>-7.417840066745788</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.244295667685138</v>
       </c>
       <c r="E17">
-        <v>-26.75260079185532</v>
+        <v>-26.37844468391957</v>
       </c>
       <c r="F17">
-        <v>0.5258060616794784</v>
+        <v>0.2011216595803926</v>
       </c>
       <c r="G17">
-        <v>-7.116322055205294</v>
+        <v>-7.024060667396827</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.301947232323809</v>
       </c>
       <c r="E18">
-        <v>-28.07037314266537</v>
+        <v>-27.69735368170555</v>
       </c>
       <c r="F18">
-        <v>0.8115157774768476</v>
+        <v>0.1782852270200158</v>
       </c>
       <c r="G18">
-        <v>-6.821632265730004</v>
+        <v>-7.334014699566653</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-2.407286021946648</v>
       </c>
       <c r="E19">
-        <v>-27.97067878738651</v>
+        <v>-27.68373203189048</v>
       </c>
       <c r="F19">
-        <v>1.196126762596658</v>
+        <v>0.2985923383981993</v>
       </c>
       <c r="G19">
-        <v>-6.252432199370011</v>
+        <v>-7.374626378807901</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-2.547769321298411</v>
       </c>
       <c r="E20">
-        <v>-29.37657071391182</v>
+        <v>-27.50164662051606</v>
       </c>
       <c r="F20">
-        <v>1.422380408058093</v>
+        <v>1.163296905688908</v>
       </c>
       <c r="G20">
-        <v>-6.506723589005417</v>
+        <v>-7.208448912929823</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-2.717492539735491</v>
       </c>
       <c r="E21">
-        <v>-29.8632752505972</v>
+        <v>-29.67483412595302</v>
       </c>
       <c r="F21">
-        <v>1.893090244290078</v>
+        <v>1.277886625252969</v>
       </c>
       <c r="G21">
-        <v>-7.880164184471548</v>
+        <v>-7.454373187588645</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.899117926553616</v>
       </c>
       <c r="E22">
-        <v>-30.80348381678073</v>
+        <v>-28.59839774043374</v>
       </c>
       <c r="F22">
-        <v>1.816454662387485</v>
+        <v>0.5995928880838444</v>
       </c>
       <c r="G22">
-        <v>-7.105110121136671</v>
+        <v>-6.134875874559785</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-3.076890135584283</v>
       </c>
       <c r="E23">
-        <v>-29.81336920279567</v>
+        <v>-31.02944108434146</v>
       </c>
       <c r="F23">
-        <v>2.228474668131125</v>
+        <v>2.251423758658282</v>
       </c>
       <c r="G23">
-        <v>-7.005475828484133</v>
+        <v>-7.010017039122403</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-3.2300598304465</v>
       </c>
       <c r="E24">
-        <v>-31.29129330112399</v>
+        <v>-29.91070195887953</v>
       </c>
       <c r="F24">
-        <v>2.552825238166883</v>
+        <v>1.66504235503418</v>
       </c>
       <c r="G24">
-        <v>-6.508232950922761</v>
+        <v>-6.294966674445092</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-3.338226268112083</v>
       </c>
       <c r="E25">
-        <v>-30.44040662050475</v>
+        <v>-32.01000967511835</v>
       </c>
       <c r="F25">
-        <v>2.308650692313284</v>
+        <v>1.777327556483653</v>
       </c>
       <c r="G25">
-        <v>-6.941918566877688</v>
+        <v>-6.27778619835984</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-3.389940329690672</v>
       </c>
       <c r="E26">
-        <v>-31.63900538509194</v>
+        <v>-32.41767422647386</v>
       </c>
       <c r="F26">
-        <v>2.13613821047587</v>
+        <v>2.382151731963684</v>
       </c>
       <c r="G26">
-        <v>-6.447884724001455</v>
+        <v>-6.582329496178142</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.375736584152782</v>
       </c>
       <c r="E27">
-        <v>-31.39262922823063</v>
+        <v>-31.44353606878786</v>
       </c>
       <c r="F27">
-        <v>2.604488856344682</v>
+        <v>1.876406924797696</v>
       </c>
       <c r="G27">
-        <v>-7.257378488824263</v>
+        <v>-7.248955593081168</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.298480769639353</v>
       </c>
       <c r="E28">
-        <v>-30.32569358117945</v>
+        <v>-31.70677852709074</v>
       </c>
       <c r="F28">
-        <v>2.509521503818136</v>
+        <v>2.227430925203598</v>
       </c>
       <c r="G28">
-        <v>-6.928189935872972</v>
+        <v>-6.65112358739346</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.164239887529515</v>
       </c>
       <c r="E29">
-        <v>-31.2983282854949</v>
+        <v>-31.39173259037711</v>
       </c>
       <c r="F29">
-        <v>2.207637914481106</v>
+        <v>1.575263895918769</v>
       </c>
       <c r="G29">
-        <v>-6.531949620354427</v>
+        <v>-6.905854660717831</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.985991936033972</v>
       </c>
       <c r="E30">
-        <v>-29.7372274408307</v>
+        <v>-31.17890336896462</v>
       </c>
       <c r="F30">
-        <v>2.124100375378387</v>
+        <v>2.083629657547215</v>
       </c>
       <c r="G30">
-        <v>-6.82213101140704</v>
+        <v>-6.026953216248089</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.781390641659687</v>
       </c>
       <c r="E31">
-        <v>-30.64320074351624</v>
+        <v>-31.74993941285784</v>
       </c>
       <c r="F31">
-        <v>2.186797847361476</v>
+        <v>1.95419062392057</v>
       </c>
       <c r="G31">
-        <v>-6.086845353372633</v>
+        <v>-6.686760934750589</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-2.565883931751594</v>
       </c>
       <c r="E32">
-        <v>-30.6862733240402</v>
+        <v>-30.4330569071903</v>
       </c>
       <c r="F32">
-        <v>1.852869693414551</v>
+        <v>1.327548907785605</v>
       </c>
       <c r="G32">
-        <v>-6.143325020075355</v>
+        <v>-5.681525897799106</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.358605068793824</v>
       </c>
       <c r="E33">
-        <v>-29.93258354528459</v>
+        <v>-29.92310997766055</v>
       </c>
       <c r="F33">
-        <v>1.913917057531263</v>
+        <v>1.345294194288376</v>
       </c>
       <c r="G33">
-        <v>-6.188461503847076</v>
+        <v>-6.215406895293237</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.170838091248547</v>
       </c>
       <c r="E34">
-        <v>-30.00452514760745</v>
+        <v>-28.75083070400593</v>
       </c>
       <c r="F34">
-        <v>1.796852176167637</v>
+        <v>1.751822124151456</v>
       </c>
       <c r="G34">
-        <v>-6.414235796909349</v>
+        <v>-6.267315820363652</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.011694213650252</v>
       </c>
       <c r="E35">
-        <v>-29.76315521876161</v>
+        <v>-29.61852934437865</v>
       </c>
       <c r="F35">
-        <v>1.773321571723714</v>
+        <v>1.113119378631731</v>
       </c>
       <c r="G35">
-        <v>-5.975228039585002</v>
+        <v>-6.780892618847939</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.884961150257357</v>
       </c>
       <c r="E36">
-        <v>-29.02559133594733</v>
+        <v>-28.44928414830917</v>
       </c>
       <c r="F36">
-        <v>1.730827980694905</v>
+        <v>1.642678091893399</v>
       </c>
       <c r="G36">
-        <v>-6.585738685378405</v>
+        <v>-5.700629169718193</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-1.786018349537049</v>
       </c>
       <c r="E37">
-        <v>-29.08541700606266</v>
+        <v>-29.17002248594796</v>
       </c>
       <c r="F37">
-        <v>1.697166442914745</v>
+        <v>1.783194054430279</v>
       </c>
       <c r="G37">
-        <v>-5.860306535687011</v>
+        <v>-5.776920852196842</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-1.710860566163067</v>
       </c>
       <c r="E38">
-        <v>-27.5770638266398</v>
+        <v>-27.2918469482147</v>
       </c>
       <c r="F38">
-        <v>1.756432817115438</v>
+        <v>1.20424973334851</v>
       </c>
       <c r="G38">
-        <v>-5.584723299352368</v>
+        <v>-5.716326533658576</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.646120542164</v>
       </c>
       <c r="E39">
-        <v>-27.51134208336648</v>
+        <v>-26.55879568974905</v>
       </c>
       <c r="F39">
-        <v>1.81173959513075</v>
+        <v>1.266698695110759</v>
       </c>
       <c r="G39">
-        <v>-5.525234752479635</v>
+        <v>-6.90196313194833</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.578752564871059</v>
       </c>
       <c r="E40">
-        <v>-27.33207338282483</v>
+        <v>-25.73664670518249</v>
       </c>
       <c r="F40">
-        <v>1.484433410201804</v>
+        <v>1.632369887932962</v>
       </c>
       <c r="G40">
-        <v>-5.885726159108029</v>
+        <v>-6.111287172768937</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.494949621407319</v>
       </c>
       <c r="E41">
-        <v>-27.77695519781238</v>
+        <v>-26.14865179887435</v>
       </c>
       <c r="F41">
-        <v>1.694542174982676</v>
+        <v>1.146741154776557</v>
       </c>
       <c r="G41">
-        <v>-5.632428979605135</v>
+        <v>-6.593203464426142</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.381228332593109</v>
       </c>
       <c r="E42">
-        <v>-26.90753347307975</v>
+        <v>-25.56875805982212</v>
       </c>
       <c r="F42">
-        <v>1.678413861650169</v>
+        <v>1.044131284591782</v>
       </c>
       <c r="G42">
-        <v>-5.753099183675273</v>
+        <v>-6.579819361685167</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.231521813605681</v>
       </c>
       <c r="E43">
-        <v>-25.86909551295883</v>
+        <v>-26.06421387252733</v>
       </c>
       <c r="F43">
-        <v>1.539132166543461</v>
+        <v>1.550964566525049</v>
       </c>
       <c r="G43">
-        <v>-5.843355745110919</v>
+        <v>-6.138121002682076</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.041568586751963</v>
       </c>
       <c r="E44">
-        <v>-25.14062254171494</v>
+        <v>-25.78240240655599</v>
       </c>
       <c r="F44">
-        <v>1.746671335640849</v>
+        <v>0.7139191868138154</v>
       </c>
       <c r="G44">
-        <v>-5.479317337976766</v>
+        <v>-6.29835289509444</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.8148034615977923</v>
       </c>
       <c r="E45">
-        <v>-25.4581681960808</v>
+        <v>-26.19782649812364</v>
       </c>
       <c r="F45">
-        <v>1.582298391903343</v>
+        <v>0.7192273651309546</v>
       </c>
       <c r="G45">
-        <v>-5.925258316456219</v>
+        <v>-5.421246278817713</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.5589652415500671</v>
       </c>
       <c r="E46">
-        <v>-24.96497662037943</v>
+        <v>-22.64467257985529</v>
       </c>
       <c r="F46">
-        <v>1.603307445973144</v>
+        <v>1.467882629493869</v>
       </c>
       <c r="G46">
-        <v>-5.373639035211729</v>
+        <v>-5.704103983349645</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.2840719232209789</v>
       </c>
       <c r="E47">
-        <v>-24.50483837646005</v>
+        <v>-25.25836739438838</v>
       </c>
       <c r="F47">
-        <v>1.340501260495778</v>
+        <v>0.895530456203579</v>
       </c>
       <c r="G47">
-        <v>-5.718981041900167</v>
+        <v>-5.517983252833262</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.004393209978849078</v>
       </c>
       <c r="E48">
-        <v>-23.80033914661276</v>
+        <v>-23.58956132392574</v>
       </c>
       <c r="F48">
-        <v>1.445597889623757</v>
+        <v>1.425780027879182</v>
       </c>
       <c r="G48">
-        <v>-5.7050785061528</v>
+        <v>-5.949555762103906</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>0.2683392498247185</v>
       </c>
       <c r="E49">
-        <v>-23.35158095787465</v>
+        <v>-23.18803511908764</v>
       </c>
       <c r="F49">
-        <v>1.54258811534794</v>
+        <v>0.9438093651735397</v>
       </c>
       <c r="G49">
-        <v>-5.332456423419139</v>
+        <v>-6.357283634302067</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>0.5209719311427528</v>
       </c>
       <c r="E50">
-        <v>-22.60664698361288</v>
+        <v>-21.35194721878166</v>
       </c>
       <c r="F50">
-        <v>1.363523247354382</v>
+        <v>1.503934835598509</v>
       </c>
       <c r="G50">
-        <v>-6.251362521141631</v>
+        <v>-6.83850430698867</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>0.7439655758336813</v>
       </c>
       <c r="E51">
-        <v>-22.56169735061274</v>
+        <v>-21.23551109509644</v>
       </c>
       <c r="F51">
-        <v>1.64467280059934</v>
+        <v>1.075118852395706</v>
       </c>
       <c r="G51">
-        <v>-6.43325047584633</v>
+        <v>-6.259434326177866</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>0.9302933016058159</v>
       </c>
       <c r="E52">
-        <v>-22.05849331888041</v>
+        <v>-22.16614873146476</v>
       </c>
       <c r="F52">
-        <v>1.749131586827163</v>
+        <v>1.146379986588936</v>
       </c>
       <c r="G52">
-        <v>-6.47260872845187</v>
+        <v>-6.118459923097883</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>1.074988498360165</v>
       </c>
       <c r="E53">
-        <v>-21.26656284136703</v>
+        <v>-21.68926419066501</v>
       </c>
       <c r="F53">
-        <v>1.61299106091187</v>
+        <v>1.260835510633744</v>
       </c>
       <c r="G53">
-        <v>-6.026805561277913</v>
+        <v>-6.002334210887575</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>1.177075144726486</v>
       </c>
       <c r="E54">
-        <v>-21.07967724754449</v>
+        <v>-19.25064923821647</v>
       </c>
       <c r="F54">
-        <v>1.409428055347919</v>
+        <v>0.6846074062657549</v>
       </c>
       <c r="G54">
-        <v>-6.662479895210698</v>
+        <v>-5.528712847332646</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>1.236003690784304</v>
       </c>
       <c r="E55">
-        <v>-21.40872522588983</v>
+        <v>-20.31008120383694</v>
       </c>
       <c r="F55">
-        <v>1.530399517383148</v>
+        <v>1.119040548826941</v>
       </c>
       <c r="G55">
-        <v>-6.475227143256307</v>
+        <v>-6.190991325669408</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>1.254426013908175</v>
       </c>
       <c r="E56">
-        <v>-19.81484728635811</v>
+        <v>-19.43152554703084</v>
       </c>
       <c r="F56">
-        <v>1.444670118132622</v>
+        <v>1.011652655462819</v>
       </c>
       <c r="G56">
-        <v>-6.894760850625349</v>
+        <v>-6.0245251122941</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>1.235426280114984</v>
       </c>
       <c r="E57">
-        <v>-20.35907929259993</v>
+        <v>-20.96036554286439</v>
       </c>
       <c r="F57">
-        <v>1.2712381484781</v>
+        <v>0.6640183344691731</v>
       </c>
       <c r="G57">
-        <v>-6.989801433094665</v>
+        <v>-6.966832882178552</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>1.183192332218197</v>
       </c>
       <c r="E58">
-        <v>-18.40940367875956</v>
+        <v>-19.20418709489777</v>
       </c>
       <c r="F58">
-        <v>1.370773118863683</v>
+        <v>1.03531579869119</v>
       </c>
       <c r="G58">
-        <v>-6.950400524608852</v>
+        <v>-7.24870622024265</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>1.101058721387968</v>
       </c>
       <c r="E59">
-        <v>-19.92630208863489</v>
+        <v>-19.07180168575753</v>
       </c>
       <c r="F59">
-        <v>1.423347941184562</v>
+        <v>1.463280220203915</v>
       </c>
       <c r="G59">
-        <v>-7.177556211947651</v>
+        <v>-7.30289231307532</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>0.9924739446650784</v>
       </c>
       <c r="E60">
-        <v>-18.64157401265881</v>
+        <v>-17.81533128758932</v>
       </c>
       <c r="F60">
-        <v>1.336781890857208</v>
+        <v>0.9846594752751946</v>
       </c>
       <c r="G60">
-        <v>-7.290033205783857</v>
+        <v>-6.931871466462669</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>0.8598017080551532</v>
       </c>
       <c r="E61">
-        <v>-18.53089810791135</v>
+        <v>-17.9094284489947</v>
       </c>
       <c r="F61">
-        <v>1.038949018119869</v>
+        <v>0.5850475848580878</v>
       </c>
       <c r="G61">
-        <v>-7.446888721211551</v>
+        <v>-6.549750247314416</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>0.7056817822449351</v>
       </c>
       <c r="E62">
-        <v>-18.91983968348214</v>
+        <v>-18.13971946618077</v>
       </c>
       <c r="F62">
-        <v>1.083258390495614</v>
+        <v>0.8883816455174193</v>
       </c>
       <c r="G62">
-        <v>-7.369353455761873</v>
+        <v>-7.015178400635411</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>0.5329356193564179</v>
       </c>
       <c r="E63">
-        <v>-18.1704361053748</v>
+        <v>-17.14509902055807</v>
       </c>
       <c r="F63">
-        <v>1.425009646194578</v>
+        <v>0.676979799220777</v>
       </c>
       <c r="G63">
-        <v>-7.982489078802832</v>
+        <v>-8.18222687879091</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>0.3452205027318636</v>
       </c>
       <c r="E64">
-        <v>-17.05087053340647</v>
+        <v>-17.733080614188</v>
       </c>
       <c r="F64">
-        <v>1.066580041207649</v>
+        <v>0.9640944261332941</v>
       </c>
       <c r="G64">
-        <v>-7.35731793508183</v>
+        <v>-7.269948848618496</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>0.1485841272657417</v>
       </c>
       <c r="E65">
-        <v>-18.16812205515687</v>
+        <v>-16.70231388903608</v>
       </c>
       <c r="F65">
-        <v>0.8783699970871844</v>
+        <v>0.8449867907543643</v>
       </c>
       <c r="G65">
-        <v>-7.516158589552989</v>
+        <v>-8.030910065355558</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-0.05128529792224368</v>
       </c>
       <c r="E66">
-        <v>-17.78897556886468</v>
+        <v>-17.49695692248005</v>
       </c>
       <c r="F66">
-        <v>0.9508206668708348</v>
+        <v>0.6144297766353863</v>
       </c>
       <c r="G66">
-        <v>-7.995800994669499</v>
+        <v>-7.099607512581483</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-0.2458869817346759</v>
       </c>
       <c r="E67">
-        <v>-17.47003061603045</v>
+        <v>-17.8149644811947</v>
       </c>
       <c r="F67">
-        <v>1.027593757762293</v>
+        <v>-0.1067212048523765</v>
       </c>
       <c r="G67">
-        <v>-8.03012913462441</v>
+        <v>-8.021401085276286</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-0.428040648151767</v>
       </c>
       <c r="E68">
-        <v>-16.92247018139298</v>
+        <v>-16.52990129814205</v>
       </c>
       <c r="F68">
-        <v>0.928285760045077</v>
+        <v>0.2755620678655674</v>
       </c>
       <c r="G68">
-        <v>-8.236550782929076</v>
+        <v>-8.227675078610778</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-0.5888332525880287</v>
       </c>
       <c r="E69">
-        <v>-15.67752474957429</v>
+        <v>-17.04544542154528</v>
       </c>
       <c r="F69">
-        <v>0.6541541354366366</v>
+        <v>1.012668233898651</v>
       </c>
       <c r="G69">
-        <v>-7.916182153529573</v>
+        <v>-7.24876856345228</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-0.720543345959362</v>
       </c>
       <c r="E70">
-        <v>-17.18135398346348</v>
+        <v>-17.00340306885807</v>
       </c>
       <c r="F70">
-        <v>0.8495842298399016</v>
+        <v>-0.2175228002834355</v>
       </c>
       <c r="G70">
-        <v>-7.142978699154223</v>
+        <v>-7.433704772985703</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-0.815096572907516</v>
       </c>
       <c r="E71">
-        <v>-17.40977021241038</v>
+        <v>-16.38555166067355</v>
       </c>
       <c r="F71">
-        <v>0.552006494262624</v>
+        <v>0.1880417382901884</v>
       </c>
       <c r="G71">
-        <v>-7.784316421498609</v>
+        <v>-6.993752023852236</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-0.8651310983843735</v>
       </c>
       <c r="E72">
-        <v>-17.20900484575432</v>
+        <v>-15.41443399515066</v>
       </c>
       <c r="F72">
-        <v>0.4159968503969732</v>
+        <v>-0.3075679937025474</v>
       </c>
       <c r="G72">
-        <v>-7.801546115907253</v>
+        <v>-9.354266094938325</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-0.8652749144817484</v>
       </c>
       <c r="E73">
-        <v>-17.71852157025334</v>
+        <v>-15.74515750887884</v>
       </c>
       <c r="F73">
-        <v>0.4668337579067788</v>
+        <v>-0.03235783473566204</v>
       </c>
       <c r="G73">
-        <v>-7.61707583983527</v>
+        <v>-7.856844542848575</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-0.8098694876755169</v>
       </c>
       <c r="E74">
-        <v>-16.6138275069262</v>
+        <v>-15.96710707694278</v>
       </c>
       <c r="F74">
-        <v>0.4396293440314403</v>
+        <v>0.02725728214160998</v>
       </c>
       <c r="G74">
-        <v>-7.128734916364674</v>
+        <v>-7.877086398648789</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-0.6980448675906743</v>
       </c>
       <c r="E75">
-        <v>-16.57328860760954</v>
+        <v>-16.80018779776386</v>
       </c>
       <c r="F75">
-        <v>0.5298128748068196</v>
+        <v>0.2067644983282629</v>
       </c>
       <c r="G75">
-        <v>-7.784300015390811</v>
+        <v>-8.512478547527461</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-0.526470079984081</v>
       </c>
       <c r="E76">
-        <v>-18.36692659256761</v>
+        <v>-17.02861761213278</v>
       </c>
       <c r="F76">
-        <v>0.2500624341051902</v>
+        <v>-0.7122204997656891</v>
       </c>
       <c r="G76">
-        <v>-6.939628274229196</v>
+        <v>-7.981704866850124</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-0.2973209609730217</v>
       </c>
       <c r="E77">
-        <v>-17.86468259732491</v>
+        <v>-17.55317339881127</v>
       </c>
       <c r="F77">
-        <v>0.2032373099271426</v>
+        <v>0.158217198319795</v>
       </c>
       <c r="G77">
-        <v>-6.97441250398087</v>
+        <v>-6.068834728232841</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-0.0110448382605851</v>
       </c>
       <c r="E78">
-        <v>-18.11451397985407</v>
+        <v>-16.7674469306884</v>
       </c>
       <c r="F78">
-        <v>0.06599257026391767</v>
+        <v>-0.8071265531044285</v>
       </c>
       <c r="G78">
-        <v>-7.006145197682259</v>
+        <v>-7.693797362338207</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>0.3280255443904745</v>
       </c>
       <c r="E79">
-        <v>-18.81887735548113</v>
+        <v>-18.96043745296091</v>
       </c>
       <c r="F79">
-        <v>-0.04878104686356504</v>
+        <v>-0.4011594279730439</v>
       </c>
       <c r="G79">
-        <v>-6.923996534720001</v>
+        <v>-7.795905696046567</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>0.7118729547517532</v>
       </c>
       <c r="E80">
-        <v>-19.66049424980666</v>
+        <v>-17.58475950501477</v>
       </c>
       <c r="F80">
-        <v>0.2250987540544243</v>
+        <v>-0.7273249509883353</v>
       </c>
       <c r="G80">
-        <v>-6.409802866582539</v>
+        <v>-5.74484691145327</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>1.133874093430179</v>
       </c>
       <c r="E81">
-        <v>-19.94625001663868</v>
+        <v>-18.78838261151348</v>
       </c>
       <c r="F81">
-        <v>0.08256406015692178</v>
+        <v>-0.196945325630493</v>
       </c>
       <c r="G81">
-        <v>-6.327421236889561</v>
+        <v>-6.205884790327728</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>1.579096509332989</v>
       </c>
       <c r="E82">
-        <v>-19.56329961218004</v>
+        <v>-20.02662137332682</v>
       </c>
       <c r="F82">
-        <v>-0.2232724984262669</v>
+        <v>-1.061601847611839</v>
       </c>
       <c r="G82">
-        <v>-6.147190299072381</v>
+        <v>-5.376142607261586</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>2.039691909196757</v>
       </c>
       <c r="E83">
-        <v>-20.23559686335878</v>
+        <v>-21.11916554089137</v>
       </c>
       <c r="F83">
-        <v>0.05547810282018354</v>
+        <v>-0.6049046743656104</v>
       </c>
       <c r="G83">
-        <v>-5.93913460243111</v>
+        <v>-7.147890687828712</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>2.50171332689432</v>
       </c>
       <c r="E84">
-        <v>-21.64313715442288</v>
+        <v>-20.27390322498966</v>
       </c>
       <c r="F84">
-        <v>-0.2544025454234723</v>
+        <v>-0.3758503187153107</v>
       </c>
       <c r="G84">
-        <v>-5.476022991531083</v>
+        <v>-6.58570587316281</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>2.953636695868215</v>
       </c>
       <c r="E85">
-        <v>-22.33324489387379</v>
+        <v>-22.22302183652709</v>
       </c>
       <c r="F85">
-        <v>-0.1561300069597558</v>
+        <v>-1.24586057922095</v>
       </c>
       <c r="G85">
-        <v>-5.48337292782424</v>
+        <v>-5.584342677651472</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>3.385058156560927</v>
       </c>
       <c r="E86">
-        <v>-23.81663712456637</v>
+        <v>-22.93292806433954</v>
       </c>
       <c r="F86">
-        <v>-0.5857511632780802</v>
+        <v>-0.6043645788189851</v>
       </c>
       <c r="G86">
-        <v>-5.591289023692816</v>
+        <v>-5.553561538202321</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>3.781354164878278</v>
       </c>
       <c r="E87">
-        <v>-24.8521949752184</v>
+        <v>-25.87186241057752</v>
       </c>
       <c r="F87">
-        <v>-0.5029425874898248</v>
+        <v>-1.020554586068318</v>
       </c>
       <c r="G87">
-        <v>-5.32630741421674</v>
+        <v>-5.203547072013235</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>4.134522805832541</v>
       </c>
       <c r="E88">
-        <v>-25.6717129163865</v>
+        <v>-24.89844428025874</v>
       </c>
       <c r="F88">
-        <v>-0.2664312684795239</v>
+        <v>-1.198425776634442</v>
       </c>
       <c r="G88">
-        <v>-4.934089876330075</v>
+        <v>-6.127112504350139</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>4.432029248211032</v>
       </c>
       <c r="E89">
-        <v>-26.91104304043569</v>
+        <v>-28.37916525677441</v>
       </c>
       <c r="F89">
-        <v>-0.6065862601932933</v>
+        <v>-0.83211259907507</v>
       </c>
       <c r="G89">
-        <v>-5.608735278724384</v>
+        <v>-4.882450011427534</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>4.667098147515954</v>
       </c>
       <c r="E90">
-        <v>-27.93906098186496</v>
+        <v>-28.57637124286043</v>
       </c>
       <c r="F90">
-        <v>-0.7756643307787005</v>
+        <v>-1.130745674723514</v>
       </c>
       <c r="G90">
-        <v>-4.83567291687609</v>
+        <v>-5.273128656402819</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>4.835606589687395</v>
       </c>
       <c r="E91">
-        <v>-29.3619799706591</v>
+        <v>-29.68711987593583</v>
       </c>
       <c r="F91">
-        <v>-0.9090364528338376</v>
+        <v>-1.672950244756319</v>
       </c>
       <c r="G91">
-        <v>-4.892687422693002</v>
+        <v>-4.832490131963429</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>4.933487608165147</v>
       </c>
       <c r="E92">
-        <v>-31.94074666517103</v>
+        <v>-31.8494503649394</v>
       </c>
       <c r="F92">
-        <v>-1.14213075630759</v>
+        <v>-1.759499727735617</v>
       </c>
       <c r="G92">
-        <v>-4.468464849715513</v>
+        <v>-4.986956918095848</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>4.962677749877377</v>
       </c>
       <c r="E93">
-        <v>-32.24877120293577</v>
+        <v>-32.06831604220411</v>
       </c>
       <c r="F93">
-        <v>-1.096441323838781</v>
+        <v>-1.94216716556395</v>
       </c>
       <c r="G93">
-        <v>-4.867267799271984</v>
+        <v>-4.77983308837746</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>4.920635512475153</v>
       </c>
       <c r="E94">
-        <v>-34.66886469669294</v>
+        <v>-35.47393227730257</v>
       </c>
       <c r="F94">
-        <v>-1.258269522914887</v>
+        <v>-2.647334798014696</v>
       </c>
       <c r="G94">
-        <v>-5.651177879595801</v>
+        <v>-5.593959938042205</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>4.811775267877187</v>
       </c>
       <c r="E95">
-        <v>-36.2856159584374</v>
+        <v>-37.19508071458286</v>
       </c>
       <c r="F95">
-        <v>-1.431887875235038</v>
+        <v>-1.98561669257559</v>
       </c>
       <c r="G95">
-        <v>-4.712262892803815</v>
+        <v>-5.976524122100983</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>4.635752297024965</v>
       </c>
       <c r="E96">
-        <v>-38.07299332807987</v>
+        <v>-37.42634082520657</v>
       </c>
       <c r="F96">
-        <v>-1.679216015791095</v>
+        <v>-2.273789973028885</v>
       </c>
       <c r="G96">
-        <v>-5.377317284579867</v>
+        <v>-5.754319798095387</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>4.400958916684337</v>
       </c>
       <c r="E97">
-        <v>-39.82965179429131</v>
+        <v>-41.6635048926745</v>
       </c>
       <c r="F97">
-        <v>-1.780665343244547</v>
+        <v>-2.398601746343492</v>
       </c>
       <c r="G97">
-        <v>-5.652939895573224</v>
+        <v>-6.168984172670212</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>4.106573417406048</v>
       </c>
       <c r="E98">
-        <v>-42.75650870035084</v>
+        <v>-42.42364548265403</v>
       </c>
       <c r="F98">
-        <v>-2.042259627211617</v>
+        <v>-2.524684235253993</v>
       </c>
       <c r="G98">
-        <v>-6.001661560467888</v>
+        <v>-5.481893096900929</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>3.775541365519532</v>
       </c>
       <c r="E99">
-        <v>-45.05842034369283</v>
+        <v>-44.82042186374571</v>
       </c>
       <c r="F99">
-        <v>-2.404816158599294</v>
+        <v>-3.308927819975981</v>
       </c>
       <c r="G99">
-        <v>-5.81800174612109</v>
+        <v>-6.355662710851701</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>3.393673970452055</v>
       </c>
       <c r="E100">
-        <v>-46.25181815588222</v>
+        <v>-46.37122948699047</v>
       </c>
       <c r="F100">
-        <v>-2.514158999034023</v>
+        <v>-2.854193877474386</v>
       </c>
       <c r="G100">
-        <v>-6.419390595979237</v>
+        <v>-6.831853270887675</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>3.017829738555821</v>
       </c>
       <c r="E101">
-        <v>-48.62664728769572</v>
+        <v>-49.26444209541002</v>
       </c>
       <c r="F101">
-        <v>-2.46851595513977</v>
+        <v>-3.475531557129226</v>
       </c>
       <c r="G101">
-        <v>-6.444337723495694</v>
+        <v>-7.418122251799899</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>2.580851529784388</v>
       </c>
       <c r="E102">
-        <v>-49.48536709622972</v>
+        <v>-50.92311683739899</v>
       </c>
       <c r="F102">
-        <v>-2.608454545596899</v>
+        <v>-2.943385852468615</v>
       </c>
       <c r="G102">
-        <v>-7.198851339868447</v>
+        <v>-7.689453024993503</v>
       </c>
     </row>
   </sheetData>
